--- a/Team-Data/2012-13/1-5-2012-13.xlsx
+++ b/Team-Data/2012-13/1-5-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.625</v>
+        <v>0.645</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="P2" t="n">
         <v>19.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.707</v>
+        <v>0.705</v>
       </c>
       <c r="R2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="V2" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="W2" t="n">
         <v>8.800000000000001</v>
@@ -727,19 +794,19 @@
         <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -754,10 +821,10 @@
         <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
@@ -784,22 +851,22 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -811,10 +878,10 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.485</v>
+        <v>0.469</v>
       </c>
       <c r="H3" t="n">
         <v>48.9</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.46</v>
@@ -873,34 +940,34 @@
         <v>15.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.345</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="R3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T3" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="U3" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
         <v>14.4</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
         <v>4</v>
@@ -909,22 +976,22 @@
         <v>5.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>17</v>
@@ -936,10 +1003,10 @@
         <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>6</v>
@@ -951,49 +1018,49 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="L4" t="n">
         <v>7.5</v>
@@ -1055,61 +1122,61 @@
         <v>21.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S4" t="n">
         <v>29.3</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
         <v>18.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>11</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1118,13 +1185,13 @@
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1133,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1142,28 +1209,28 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX4" t="n">
         <v>19</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
@@ -1172,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1297,10 +1364,10 @@
         <v>27</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
         <v>13</v>
@@ -1315,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
@@ -1324,22 +1391,22 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1354,10 +1421,10 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1467,25 +1534,25 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
@@ -1497,10 +1564,10 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1515,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -1527,13 +1594,13 @@
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
         <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1571,49 +1638,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.229</v>
+        <v>0.235</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="L7" t="n">
         <v>7.7</v>
       </c>
       <c r="M7" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P7" t="n">
         <v>21.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="O7" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.742</v>
+        <v>0.736</v>
       </c>
       <c r="R7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S7" t="n">
         <v>29</v>
@@ -1628,28 +1695,28 @@
         <v>15.3</v>
       </c>
       <c r="W7" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
         <v>3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.5</v>
+        <v>94.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1658,7 +1725,7 @@
         <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
@@ -1667,7 +1734,7 @@
         <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1679,16 +1746,16 @@
         <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
@@ -1706,7 +1773,7 @@
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1715,13 +1782,13 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.382</v>
+        <v>0.394</v>
       </c>
       <c r="H8" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="I8" t="n">
         <v>37.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.447</v>
@@ -1786,19 +1853,19 @@
         <v>0.356</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P8" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T8" t="n">
         <v>41.5</v>
@@ -1807,13 +1874,13 @@
         <v>21.8</v>
       </c>
       <c r="V8" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y8" t="n">
         <v>4.5</v>
@@ -1822,16 +1889,16 @@
         <v>21.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC8" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
@@ -1843,19 +1910,19 @@
         <v>21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>14</v>
@@ -1864,10 +1931,10 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP8" t="n">
         <v>19</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>21</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
@@ -1879,19 +1946,19 @@
         <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
@@ -1900,13 +1967,13 @@
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.543</v>
+        <v>0.529</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,46 +2020,46 @@
         <v>39.3</v>
       </c>
       <c r="J9" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M9" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="O9" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.68</v>
+        <v>0.678</v>
       </c>
       <c r="R9" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="S9" t="n">
         <v>32.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="U9" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X9" t="n">
         <v>6.7</v>
@@ -2004,22 +2071,22 @@
         <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.7</v>
+        <v>101.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>11</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
@@ -2031,64 +2098,64 @@
         <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,10 +2271,10 @@
         <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2216,10 +2283,10 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
         <v>27</v>
@@ -2237,7 +2304,7 @@
         <v>26</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>12</v>
@@ -2249,7 +2316,7 @@
         <v>26</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
@@ -2261,10 +2328,10 @@
         <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -2299,115 +2366,115 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
         <v>22</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.667</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="J11" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.386</v>
+        <v>0.391</v>
       </c>
       <c r="O11" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="U11" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
         <v>15.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AA11" t="n">
         <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.4</v>
+        <v>101.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
         <v>5</v>
       </c>
-      <c r="AF11" t="n">
-        <v>7</v>
-      </c>
       <c r="AG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" t="n">
         <v>6</v>
       </c>
-      <c r="AH11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
         <v>12</v>
@@ -2419,13 +2486,13 @@
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -2434,25 +2501,25 @@
         <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -2481,52 +2548,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.588</v>
+        <v>0.576</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I12" t="n">
         <v>38.3</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="N12" t="n">
         <v>0.359</v>
       </c>
       <c r="O12" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="P12" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R12" t="n">
         <v>10.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.3</v>
@@ -2538,46 +2605,46 @@
         <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF12" t="n">
         <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK12" t="n">
         <v>7</v>
@@ -2589,16 +2656,16 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
         <v>21</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>26</v>
@@ -2625,16 +2692,16 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.588</v>
+        <v>0.576</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.5</v>
+        <v>80.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
         <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.731</v>
+        <v>0.734</v>
       </c>
       <c r="R13" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="S13" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T13" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W13" t="n">
         <v>6.4</v>
@@ -2726,31 +2793,31 @@
         <v>6.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
         <v>15</v>
@@ -2759,43 +2826,43 @@
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM13" t="n">
         <v>19</v>
       </c>
-      <c r="AM13" t="n">
-        <v>18</v>
-      </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,13 +2871,13 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -2845,85 +2912,85 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.771</v>
+        <v>0.765</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O14" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P14" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
         <v>0.713</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W14" t="n">
         <v>10.8</v>
       </c>
       <c r="X14" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
         <v>21.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2938,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,37 +3014,37 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>27</v>
       </c>
       <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT14" t="n">
         <v>17</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>18</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
         <v>25</v>
@@ -2995,7 +3062,7 @@
         <v>3</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3159,7 +3226,7 @@
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>22</v>
@@ -3171,7 +3238,7 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3363,7 @@
         <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
@@ -3323,7 +3390,7 @@
         <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3332,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>22</v>
@@ -3353,13 +3420,13 @@
         <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3481,10 +3548,10 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,19 +3569,19 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3526,16 +3593,16 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J18" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>17.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0.747</v>
@@ -3618,19 +3685,19 @@
         <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="T18" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.6</v>
       </c>
       <c r="W18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X18" t="n">
         <v>7.3</v>
@@ -3639,28 +3706,28 @@
         <v>4.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
         <v>19.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3690,40 +3757,40 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT18" t="n">
         <v>9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>14</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.43</v>
@@ -3782,64 +3849,64 @@
         <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N19" t="n">
         <v>0.295</v>
       </c>
       <c r="O19" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="R19" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="S19" t="n">
         <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="U19" t="n">
         <v>21.7</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W19" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X19" t="n">
         <v>5.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA19" t="n">
         <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
@@ -3851,7 +3918,7 @@
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3866,31 +3933,31 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.242</v>
+        <v>0.219</v>
       </c>
       <c r="H20" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.441</v>
@@ -3964,7 +4031,7 @@
         <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N20" t="n">
         <v>0.379</v>
@@ -3973,61 +4040,61 @@
         <v>14.3</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T20" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U20" t="n">
         <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W20" t="n">
         <v>6.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="AA20" t="n">
         <v>18.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
         <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4036,19 +4103,19 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN20" t="n">
         <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>28</v>
@@ -4057,10 +4124,10 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
@@ -4069,22 +4136,22 @@
         <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>0.697</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J21" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
         <v>11.3</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O21" t="n">
         <v>15.8</v>
@@ -4158,7 +4225,7 @@
         <v>21.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
@@ -4170,16 +4237,16 @@
         <v>39.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="W21" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
         <v>3.9</v>
@@ -4191,13 +4258,13 @@
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.5</v>
+        <v>102.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4209,16 +4276,16 @@
         <v>5</v>
       </c>
       <c r="AH21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,34 +4294,34 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR21" t="n">
         <v>22</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>23</v>
-      </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4406,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
         <v>1</v>
@@ -4427,16 +4494,16 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.364</v>
+        <v>0.375</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>82.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M23" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O23" t="n">
         <v>12.8</v>
@@ -4525,43 +4592,43 @@
         <v>0.778</v>
       </c>
       <c r="R23" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S23" t="n">
         <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U23" t="n">
         <v>22.5</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
         <v>5.9</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
         <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.7</v>
+        <v>93.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>24</v>
@@ -4570,13 +4637,13 @@
         <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4585,16 +4652,16 @@
         <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
         <v>30</v>
@@ -4609,10 +4676,10 @@
         <v>7</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4624,10 +4691,10 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.429</v>
+        <v>0.441</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
         <v>84</v>
@@ -4689,37 +4756,37 @@
         <v>0.438</v>
       </c>
       <c r="L24" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M24" t="n">
         <v>18.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="O24" t="n">
         <v>12.8</v>
       </c>
       <c r="P24" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="R24" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S24" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V24" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W24" t="n">
         <v>7.7</v>
@@ -4731,22 +4798,22 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA24" t="n">
         <v>17.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4770,13 +4837,13 @@
         <v>17</v>
       </c>
       <c r="AM24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP24" t="n">
         <v>29</v>
@@ -4788,19 +4855,19 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -4809,7 +4876,7 @@
         <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>24</v>
@@ -4937,19 +5004,19 @@
         <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
         <v>2</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
@@ -4958,16 +5025,16 @@
         <v>27</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
         <v>27</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
         <v>29</v>
@@ -4982,19 +5049,19 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
         <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.545</v>
+        <v>0.531</v>
       </c>
       <c r="H26" t="n">
         <v>48.8</v>
@@ -5047,73 +5114,73 @@
         <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M26" t="n">
         <v>23.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.344</v>
+        <v>0.334</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="P26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S26" t="n">
         <v>29.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE26" t="n">
         <v>14</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AF26" t="n">
         <v>13</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
@@ -5131,28 +5198,28 @@
         <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP26" t="n">
         <v>22</v>
       </c>
-      <c r="AO26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>22</v>
@@ -5164,22 +5231,22 @@
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>9</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>0.382</v>
+        <v>0.394</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,10 +5296,10 @@
         <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L27" t="n">
         <v>6.8</v>
@@ -5241,55 +5308,55 @@
         <v>19</v>
       </c>
       <c r="N27" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O27" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
         <v>22.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.765</v>
+        <v>0.768</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="T27" t="n">
         <v>40.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
         <v>19.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.8</v>
+        <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>21</v>
@@ -5307,10 +5374,10 @@
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>16</v>
@@ -5322,37 +5389,37 @@
         <v>12</v>
       </c>
       <c r="AO27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP27" t="n">
         <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS27" t="n">
         <v>30</v>
       </c>
       <c r="AT27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ27" t="n">
         <v>23</v>
@@ -5361,10 +5428,10 @@
         <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.743</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,7 +5478,7 @@
         <v>39.8</v>
       </c>
       <c r="J28" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.484</v>
@@ -5423,7 +5490,7 @@
         <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.389</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
@@ -5432,16 +5499,16 @@
         <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R28" t="n">
         <v>8.5</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="T28" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U28" t="n">
         <v>25.3</v>
@@ -5450,7 +5517,7 @@
         <v>15.1</v>
       </c>
       <c r="W28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
         <v>5.2</v>
@@ -5459,16 +5526,16 @@
         <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.3</v>
+        <v>105.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,10 +5571,10 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
@@ -5519,28 +5586,28 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX28" t="n">
         <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -5653,25 +5720,25 @@
         <v>-2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5683,10 +5750,10 @@
         <v>6</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>13</v>
@@ -5695,7 +5762,7 @@
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
         <v>25</v>
@@ -5713,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
         <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J30" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L30" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="N30" t="n">
         <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P30" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R30" t="n">
         <v>13</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="X30" t="n">
         <v>6.5</v>
@@ -5823,76 +5890,76 @@
         <v>6.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX30" t="n">
         <v>6</v>
@@ -5901,10 +5968,10 @@
         <v>24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
@@ -6017,31 +6084,31 @@
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>29</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
         <v>13</v>
@@ -6059,7 +6126,7 @@
         <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>8</v>
@@ -6071,13 +6138,13 @@
         <v>21</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
         <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-5-2012-13</t>
+          <t>2013-01-05</t>
         </is>
       </c>
     </row>
